--- a/output/Databricks_Operating_Model_Jul2026.xlsx
+++ b/output/Databricks_Operating_Model_Jul2026.xlsx
@@ -826,7 +826,7 @@
     <row r="6">
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Companion to: Brick by Brick, an institutional deep dive. July 10, 2026.</t>
+          <t>Companion to: Brick by Brick, an institutional deep dive. July 10, 2026; updated July 21, 2026.</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
     <row r="21">
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sourcing: company press releases and disclosures (Sep 2024 to Jun 2026); PitchBook deal records (entity 59199-40, retrieved Jul 10, 2026); SEC EDGAR (CIK 1587468); public cloud price lists. All non-disclosed lines are labeled estimates.</t>
+          <t>Sourcing: company press releases and disclosures (Sep 2024 to Jun 2026); PitchBook deal records (entity 59199-40, retrieved Jul 21, 2026); SEC EDGAR (CIK 1587468); public cloud price lists. All non-disclosed lines are labeled estimates.</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
     <row r="110">
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Lifetime: ~$29.5B total = ~$20.2B equity + ~$9.3B debt (PitchBook 21-deal record, retrieved Jul 10, 2026). Reported $165-175B round (Jun 2026) unclosed; excluded everywhere.</t>
+          <t>Lifetime: ~$29.5B total = ~$20.2B equity + ~$9.3B debt (PitchBook 21-deal record, retrieved Jul 21, 2026). Announced $188B round (Coatue-led, signed Jul 16, 2026) unclosed; excluded everywhere.</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Anchored on the completed $134B mark (Feb 9, 2026). The reported $165-175B round is a reference, not an input. The quality-valuation correlation is embargoed; only the per-point spread is expressed.</t>
+          <t>Anchored on the completed $134B mark (Feb 9, 2026). The announced $188B round (signed Jul 16, 2026, unclosed) is a reference, not an input. The quality-valuation correlation is embargoed; only the per-point spread is expressed.</t>
         </is>
       </c>
     </row>
